--- a/Result/profitability/5314.xlsx
+++ b/Result/profitability/5314.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>1.90625</v>
+        <v>1.83375</v>
       </c>
       <c r="N2" t="n">
-        <v>54.8725</v>
+        <v>53.98375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.16</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7775</v>
+        <v>0.7275</v>
       </c>
       <c r="N3" t="n">
-        <v>53.76125</v>
+        <v>50.44125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>-0.38</v>
       </c>
       <c r="M4" t="n">
-        <v>0.64375</v>
+        <v>0.5825</v>
       </c>
       <c r="N4" t="n">
-        <v>50.76625</v>
+        <v>45.64749999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>0.49875</v>
+        <v>0.4350000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>44.14</v>
+        <v>43.72</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.38625</v>
+        <v>0.2862500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>46.17125</v>
+        <v>43.42</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.265</v>
+        <v>-0.06</v>
       </c>
       <c r="N7" t="n">
-        <v>45.44375</v>
+        <v>44.6275</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.09</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.08499999999999995</v>
+        <v>-0.095</v>
       </c>
       <c r="N8" t="n">
-        <v>46.99875</v>
+        <v>47.0975</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.04</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1262499999999999</v>
+        <v>-0.12625</v>
       </c>
       <c r="N9" t="n">
         <v>51.035</v>
@@ -1772,10 +1772,10 @@
         <v>-0.08</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.09624999999999995</v>
+        <v>-0.09625</v>
       </c>
       <c r="N11" t="n">
-        <v>55.81875</v>
+        <v>55.81874999999999</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>0.27</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.01499999999999994</v>
+        <v>-0.015</v>
       </c>
       <c r="N12" t="n">
         <v>56.7625</v>
@@ -2026,7 +2026,7 @@
         <v>1.04</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1625000000000001</v>
+        <v>0.1625</v>
       </c>
       <c r="N13" t="n">
         <v>59.93375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>5314</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1580</v>
+      </c>
+      <c r="D75" t="n">
+        <v>915</v>
+      </c>
+      <c r="E75" t="n">
+        <v>665</v>
+      </c>
+      <c r="F75" t="n">
+        <v>42.08</v>
+      </c>
+      <c r="G75" t="n">
+        <v>211</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.34%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>6</v>
+      </c>
+      <c r="J75" t="n">
+        <v>217</v>
+      </c>
+      <c r="K75" t="n">
+        <v>83</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.9725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>55.29625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.08000000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2162162162162162</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.7899999999999991</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01913296197626546</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6375000000000001</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.359999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.073943661971831</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
